--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260731.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>305,942,478</t>
+          <t>89,147,891</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>89,147,891</t>
+          <t>305,942,478</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>261,794,772</t>
+          <t>26,661,272</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>26,661,272</t>
+          <t>261,794,772</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
